--- a/stories/arbres/ATOM-LAN.MOT.001-06.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gabin est dans le salon avec papa. Sur le tapis : une pomme, une banane, une chaussette, un bonnet. Papa dit : on nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les habits. Gabin met la pomme et la banane dans le panier. Catégorie des fruits. Il met la chaussette et le bonnet sur la chaise. Catégorie des habits.</t>
+          <t>Gabin est dans le salon avec papa. Sur le tapis : une pomme, une banane, une chaussette, un bonnet. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les habits. Gabin met la pomme et la banane dans le panier. Catégorie des fruits. Il met la chaussette et le bonnet sur la chaise. Catégorie des habits.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Gabin est dans le salon avec papa. Sur le tapis : une pomme, une banane, une chaussette, un bonnet.
+papa|On nomme. On classe.
+narrateur|Une catégorie pour les fruits. Une catégorie pour les habits. Gabin met la pomme et la banane dans le panier. Catégorie des fruits. Il met la chaussette et le bonnet sur la chaise. Catégorie des habits.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Gabin range pomme et chaussette. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Gabin a classé. Une catégorie pour les fruits. Une pour les habits.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Gabin croque la pomme. Papa plie le bonnet.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-06.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Une catégorie pour les fruits. Une catégorie pour les habits. Gabin met la pomme et la banane dans le panier. Catégorie des fruits. Il met la chaussette et le bonnet sur la chaise. Catégorie des habits.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Gabin range pomme et chaussette. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Gabin a classé. Une catégorie pour les fruits. Une pour les habits.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1837,7 @@
           <t>narrateur|Gabin croque la pomme. Papa plie le bonnet.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2048,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2263,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.MOT.001-06.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gabin classe au salon</t>
+          <t>La lampe et le tapis de Victorino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sous la lampe jaune, une banane dort sur le rebord. Victorino ramasse le mélange du tapis, nomme, classe fruits et habits.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gabin est dans le salon avec papa. Sur le tapis : une pomme, une banane, une chaussette, un bonnet. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les habits. Gabin met la pomme et la banane dans le panier. Catégorie des fruits. Il met la chaussette et le bonnet sur la chaise. Catégorie des habits.</t>
+          <t>La lampe du salon fait un rond jaune. Une banane dort sur le rebord. Une chaussette dépasse sous le fauteuil. L'horloge du mur fait un bruit sourd. Un moucheron se pose sur la vitre, puis part. Le tapis sent un peu la poussière tiède. Victorino, tu as vu la banane ? Elle attend sur le rebord. Oui, papa. Elle est toute courbe. Le tapis s'est mélangé. On range avant la nuit. En ce moment, Victorino s'assoit près du fauteuil. Le tapis gratte un peu les genoux. Sur le tapis : une pomme. Une banane. Une chaussette. Un bonnet. La pomme est froide. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les habits. Victorino prend la pomme verte. Pomme. C'est un fruit. Mets-la dans le panier. Victorino pose la pomme dans le panier. Il prend la banane sur le rebord. La peau est un peu tachetée. Banane. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Victorino met la banane avec la pomme. Il tire la chaussette sous le fauteuil. Elle est un peu poussiéreuse. Chaussette. C'est un habit. Oui. Pose-la sur la chaise. Victorino pose la chaussette sur la chaise. Il prend le bonnet. Le bonnet est mou, tout chaud. Bonnet. C'est un habit. Les habits ensemble. C'est une catégorie. Victorino pose le bonnet sur la chaise. Catégorie. Fruits. Habits. Bravo, Victorino. Tu as nommé. Tu as classé. Tu as mis ensemble. C'est du bon travail. Tu as fini de ranger le tapis ? Oui, papa. Le panier a les fruits. La chaise a les habits. Le rond jaune de la lampe est plus vide, maintenant. On entend l'horloge, tout seul. Le tapis est clair.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,70 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Gabin est dans le salon avec papa. Sur le tapis : une pomme, une banane, une chaussette, un bonnet.
-papa|On nomme. On classe.
-narrateur|Une catégorie pour les fruits. Une catégorie pour les habits. Gabin met la pomme et la banane dans le panier. Catégorie des fruits. Il met la chaussette et le bonnet sur la chaise. Catégorie des habits.</t>
+          <t>narrateur|La lampe du salon fait un rond jaune.
+narrateur|Une banane dort sur le rebord.
+narrateur|Une chaussette dépasse sous le fauteuil.
+narrateur|L'horloge du mur fait un bruit sourd.
+narrateur|Un moucheron se pose sur la vitre, puis part.
+narrateur|Le tapis sent un peu la poussière tiède.
+papa|Victorino, tu as vu la banane ?
+papa|Elle attend sur le rebord.
+enfant-m|Oui, papa.
+enfant-m|Elle est toute courbe.
+papa|Le tapis s'est mélangé.
+papa|On range avant la nuit.
+narrateur|En ce moment, Victorino s'assoit près du fauteuil.
+narrateur|Le tapis gratte un peu les genoux.
+narrateur|Sur le tapis : une pomme.
+narrateur|Une banane.
+narrateur|Une chaussette.
+narrateur|Un bonnet.
+enfant-m|La pomme est froide.
+papa|On nomme.
+papa|On classe.
+papa|Une catégorie pour les fruits.
+papa|Une catégorie pour les habits.
+narrateur|Victorino prend la pomme verte.
+enfant-m|Pomme.
+enfant-m|C'est un fruit.
+papa|Mets-la dans le panier.
+narrateur|Victorino pose la pomme dans le panier.
+narrateur|Il prend la banane sur le rebord.
+narrateur|La peau est un peu tachetée.
+enfant-m|Banane.
+enfant-m|C'est un fruit aussi.
+papa|Les fruits ensemble.
+papa|C'est une catégorie.
+narrateur|Victorino met la banane avec la pomme.
+narrateur|Il tire la chaussette sous le fauteuil.
+narrateur|Elle est un peu poussiéreuse.
+enfant-m|Chaussette.
+enfant-m|C'est un habit.
+papa|Oui.
+papa|Pose-la sur la chaise.
+narrateur|Victorino pose la chaussette sur la chaise.
+narrateur|Il prend le bonnet.
+narrateur|Le bonnet est mou, tout chaud.
+enfant-m|Bonnet.
+enfant-m|C'est un habit.
+papa|Les habits ensemble.
+papa|C'est une catégorie.
+narrateur|Victorino pose le bonnet sur la chaise.
+enfant-m|Catégorie.
+enfant-m|Fruits.
+enfant-m|Habits.
+papa|Bravo, Victorino.
+papa|Tu as nommé.
+papa|Tu as classé.
+papa|Tu as mis ensemble.
+papa|C'est du bon travail.
+papa|Tu as fini de ranger le tapis ?
+enfant-m|Oui, papa.
+narrateur|Le panier a les fruits.
+narrateur|La chaise a les habits.
+narrateur|Le rond jaune de la lampe est plus vide, maintenant.
+papa|On entend l'horloge, tout seul.
+enfant-m|Le tapis est clair.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1342,7 +1415,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Gabin range pomme et chaussette. Que fait-il ?</t>
+          <t>Victorino range pomme et chaussette. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,7 +1571,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Gabin range pomme et chaussette. Que fait-il ?</t>
+          <t>narrateur|Victorino range pomme et chaussette.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1526,7 +1600,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gabin a classé. Une catégorie pour les fruits. Une pour les habits.</t>
+          <t>Victorino a classé. Une catégorie pour les fruits. Une pour les habits. Tu as mis ensemble. Bravo. C'est du bon travail, Victorino. Le panier est prêt ? Oui. Les fruits sont ensemble. Et les habits ? Sur la chaise. Le fauteuil n'a plus de chaussette dessous. Le rebord de la fenêtre est vide.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,7 +1744,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Gabin a classé. Une catégorie pour les fruits. Une pour les habits.</t>
+          <t>narrateur|Victorino a classé.
+narrateur|Une catégorie pour les fruits.
+narrateur|Une pour les habits.
+papa|Tu as mis ensemble.
+papa|Bravo.
+papa|C'est du bon travail, Victorino.
+papa|Le panier est prêt ?
+enfant-m|Oui.
+enfant-m|Les fruits sont ensemble.
+papa|Et les habits ?
+enfant-m|Sur la chaise.
+narrateur|Le fauteuil n'a plus de chaussette dessous.
+narrateur|Le rebord de la fenêtre est vide.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1698,7 +1784,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Gabin croque la pomme. Papa plie le bonnet.</t>
+          <t>Victorino croque la pomme. Elle est un peu acide, tout frais. Tu aimes ? Oui, papa. Papa plie le bonnet. Il secoue un peu la chaussette. Les habits sont ensemble. La banane reste dans le panier. On la garde pour demain ? Oui. La lampe fait toujours son rond jaune. L'horloge continue, tout sourd. Tu as classé, puis tu croques. Le salon est rangé.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1834,7 +1920,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Gabin croque la pomme. Papa plie le bonnet.</t>
+          <t>narrateur|Victorino croque la pomme.
+narrateur|Elle est un peu acide, tout frais.
+papa|Tu aimes ?
+enfant-m|Oui, papa.
+narrateur|Papa plie le bonnet.
+narrateur|Il secoue un peu la chaussette.
+papa|Les habits sont ensemble.
+enfant-m|La banane reste dans le panier.
+papa|On la garde pour demain ?
+enfant-m|Oui.
+narrateur|La lampe fait toujours son rond jaune.
+narrateur|L'horloge continue, tout sourd.
+papa|Tu as classé, puis tu croques.
+enfant-m|Le salon est rangé.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1862,7 +1961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai classé. Fruits. Habits. Bravo. Tu as fait du bon travail. Le rond jaune reste sur le tapis. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2002,7 +2101,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai classé.
+enfant-m|Fruits.
+enfant-m|Habits.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le rond jaune reste sur le tapis.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2024,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2167,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-06.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La lampe du salon fait un rond jaune. Une banane dort sur le rebord. Une chaussette dépasse sous le fauteuil. L'horloge du mur fait un bruit sourd. Un moucheron se pose sur la vitre, puis part. Le tapis sent un peu la poussière tiède. Victorino, tu as vu la banane ? Elle attend sur le rebord. Oui, papa. Elle est toute courbe. Le tapis s'est mélangé. On range avant la nuit. En ce moment, Victorino s'assoit près du fauteuil. Le tapis gratte un peu les genoux. Sur le tapis : une pomme. Une banane. Une chaussette. Un bonnet. La pomme est froide. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les habits. Victorino prend la pomme verte. Pomme. C'est un fruit. Mets-la dans le panier. Victorino pose la pomme dans le panier. Il prend la banane sur le rebord. La peau est un peu tachetée. Banane. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Victorino met la banane avec la pomme. Il tire la chaussette sous le fauteuil. Elle est un peu poussiéreuse. Chaussette. C'est un habit. Oui. Pose-la sur la chaise. Victorino pose la chaussette sur la chaise. Il prend le bonnet. Le bonnet est mou, tout chaud. Bonnet. C'est un habit. Les habits ensemble. C'est une catégorie. Victorino pose le bonnet sur la chaise. Catégorie. Fruits. Habits. Bravo, Victorino. Tu as nommé. Tu as classé. Tu as mis ensemble. C'est du bon travail. Tu as fini de ranger le tapis ? Oui, papa. Le panier a les fruits. La chaise a les habits. Le rond jaune de la lampe est plus vide, maintenant. On entend l'horloge, tout seul. Le tapis est clair.</t>
+          <t>La lampe du salon fait un rond jaune. Une banane dort sur le rebord. Une chaussette dépasse sous le fauteuil. L'horloge du mur fait un bruit sourd. Un moucheron se pose sur la vitre, puis part. Le tapis sent un peu la poussière tiède. Victorino, tu as vu la banane ? Elle attend sur le rebord. Oui, papa. Elle est toute courbe. Le tapis s'est mélangé. On range avant la nuit. En ce moment, Victorino s'assoit près du fauteuil. Le tapis gratte un peu les genoux. Sur le tapis : une pomme. Une banane. Une chaussette. Un bonnet. La pomme est froide. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les habits. Victorino prend la pomme verte. Pomme. C'est un fruit. Mets-la dans le panier. Victorino pose la pomme dans le panier. Il prend la banane sur le rebord. La peau est un peu tachetée. Banane. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Victorino met la banane avec la pomme. Il tire la chaussette sous le fauteuil. Elle est un peu poussiéreuse. Chaussette. C'est un habit. Oui. Pose-la sur la chaise. Victorino pose la chaussette sur la chaise. Il prend le bonnet. Le bonnet est mou, tout chaud. Bonnet. C'est un habit. Les habits ensemble. C'est une catégorie. Victorino pose le bonnet sur la chaise. Catégorie. Fruits. Habits. Bravo, Victorino. Tu as nommé. Tu as classé. Tu as mis ensemble. Tu as fini de ranger le tapis ? Oui, papa. Le panier a les fruits. La chaise a les habits. Le rond jaune de la lampe est plus vide, maintenant. On entend l'horloge, tout seul. Le tapis est clair.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gabin est dans le salon avec papa. Sur le tapis : une pomme, une banane, une chaussette, un bonnet. Papa dit : on nomme. On classe. Une &lt;emphasis level="moderate"&gt;catégorie&lt;/emphasis&gt; pour les fruits. Une catégorie pour les habits. Gabin met la pomme et la banane dans le panier. Catégorie des fruits. Il met la chaussette et le bonnet sur la chaise. Catégorie des habits.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La lampe du salon fait un rond jaune. Une banane dort sur le rebord. Une chaussette dépasse sous le fauteuil. L'horloge du mur fait un bruit sourd. Un moucheron se pose sur la vitre, puis part. Le tapis sent un peu la poussière tiède. Victorino, tu as vu la banane ? Elle attend sur le rebord. Oui, papa. Elle est toute courbe. Le tapis s'est mélangé. On range avant la nuit. En ce moment, Victorino s'assoit près du fauteuil. Le tapis gratte un peu les genoux. Sur le tapis : une pomme. Une banane. Une chaussette. Un bonnet. La pomme est froide. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les habits. Victorino prend la pomme verte. Pomme. C'est un fruit. Mets-la dans le panier. Victorino pose la pomme dans le panier. Il prend la banane sur le rebord. La peau est un peu tachetée. Banane. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Victorino met la banane avec la pomme. Il tire la chaussette sous le fauteuil. Elle est un peu poussiéreuse. Chaussette. C'est un habit. Oui. Pose-la sur la chaise. Victorino pose la chaussette sur la chaise. Il prend le bonnet. Le bonnet est mou, tout chaud. Bonnet. C'est un habit. Les habits ensemble. C'est une catégorie. Victorino pose le bonnet sur la chaise. Catégorie. Fruits. Habits. Bravo, Victorino. Tu as nommé. Tu as classé. Tu as mis ensemble. Tu as fini de ranger le tapis ? Oui, papa. Le panier a les fruits. La chaise a les habits. Le rond jaune de la lampe est plus vide, maintenant. On entend l'horloge, tout seul. Le tapis est clair.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1380,7 +1380,6 @@
 papa|Tu as nommé.
 papa|Tu as classé.
 papa|Tu as mis ensemble.
-papa|C'est du bon travail.
 papa|Tu as fini de ranger le tapis ?
 enfant-m|Oui, papa.
 narrateur|Le panier a les fruits.
@@ -1390,7 +1389,6 @@
 enfant-m|Le tapis est clair.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1420,7 +1418,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Gabin range pomme et chaussette. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino range pomme et chaussette. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1575,7 +1573,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1600,12 +1597,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino a classé. Une catégorie pour les fruits. Une pour les habits. Tu as mis ensemble. Bravo. C'est du bon travail, Victorino. Le panier est prêt ? Oui. Les fruits sont ensemble. Et les habits ? Sur la chaise. Le fauteuil n'a plus de chaussette dessous. Le rebord de la fenêtre est vide.</t>
+          <t>Victorino a classé. Une catégorie pour les fruits. Une pour les habits. Tu as mis ensemble. Bravo. Le panier est prêt ? Oui. Les fruits sont ensemble. Et les habits ? Sur la chaise. Le fauteuil n'a plus de chaussette dessous. Le rebord de la fenêtre est vide.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gabin a classé. Une &lt;emphasis level="moderate"&gt;catégorie&lt;/emphasis&gt; pour les fruits. Une pour les habits.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino a classé. Une catégorie pour les fruits. Une pour les habits. Tu as mis ensemble. Bravo. Le panier est prêt ? Oui. Les fruits sont ensemble. Et les habits ? Sur la chaise. Le fauteuil n'a plus de chaussette dessous. Le rebord de la fenêtre est vide.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1749,7 +1746,6 @@
 narrateur|Une pour les habits.
 papa|Tu as mis ensemble.
 papa|Bravo.
-papa|C'est du bon travail, Victorino.
 papa|Le panier est prêt ?
 enfant-m|Oui.
 enfant-m|Les fruits sont ensemble.
@@ -1759,7 +1755,6 @@
 narrateur|Le rebord de la fenêtre est vide.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1789,7 +1784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gabin croque la pomme. Papa plie le bonnet.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino croque la pomme. Elle est un peu acide, tout frais. Tu aimes ? Oui, papa. Papa plie le bonnet. Il secoue un peu la chaussette. Les habits sont ensemble. La banane reste dans le panier. On la garde pour demain ? Oui. La lampe fait toujours son rond jaune. L'horloge continue, tout sourd. Tu as classé, puis tu croques. Le salon est rangé.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1936,7 +1931,6 @@
 enfant-m|Le salon est rangé.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai classé. Fruits. Habits. Bravo. Tu as fait du bon travail. Le rond jaune reste sur le tapis. L'histoire est finie.</t>
+          <t>J'ai classé. Fruits. Habits. Bravo. Le rond jaune reste sur le tapis.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai classé. Fruits. Habits. Bravo. Le rond jaune reste sur le tapis.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2105,12 +2099,9 @@
 enfant-m|Fruits.
 enfant-m|Habits.
 papa|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Le rond jaune reste sur le tapis.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le rond jaune reste sur le tapis.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2129,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2174,6 +2165,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-06.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-06.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gabin, papa</t>
+          <t>Victorino, papa</t>
         </is>
       </c>
     </row>
